--- a/r4-ELGA-e-Medikation-Review_Architektur/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-Review_Architektur/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:41:29+00:00</t>
+    <t>2026-06-22T13:11:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
